--- a/wedding-site/Guest List Export.xlsx
+++ b/wedding-site/Guest List Export.xlsx
@@ -448,7 +448,7 @@
         <v>Ayo Abe</v>
       </c>
       <c r="D2" t="str">
-        <v>pending</v>
+        <v>submitted</v>
       </c>
       <c r="E2" t="str">
         <v>No</v>
@@ -483,19 +483,19 @@
         <v>Pelumi Abe</v>
       </c>
       <c r="D3" t="str">
-        <v>pending</v>
+        <v>submitted</v>
       </c>
       <c r="E3" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="F3" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="G3" t="str">
-        <v/>
+        <v>pelumiabe@rocketmail.com</v>
       </c>
       <c r="H3" t="str">
-        <v/>
+        <v>0798401428</v>
       </c>
       <c r="I3" t="str">
         <v>Yes</v>
@@ -518,7 +518,7 @@
         <v>Victoria Abe</v>
       </c>
       <c r="D4" t="str">
-        <v>pending</v>
+        <v>submitted</v>
       </c>
       <c r="E4" t="str">
         <v>No</v>
@@ -1428,19 +1428,19 @@
         <v>Jesudara Ilesanmi</v>
       </c>
       <c r="D30" t="str">
-        <v>pending</v>
+        <v>submitted</v>
       </c>
       <c r="E30" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="F30" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="G30" t="str">
-        <v/>
+        <v>towo.ilez@gmail.com</v>
       </c>
       <c r="H30" t="str">
-        <v/>
+        <v>+27 63 819 9263</v>
       </c>
       <c r="I30" t="str">
         <v>Yes</v>
@@ -1463,19 +1463,19 @@
         <v>Jesujoba Ilesanmi</v>
       </c>
       <c r="D31" t="str">
-        <v>pending</v>
+        <v>submitted</v>
       </c>
       <c r="E31" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="F31" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="G31" t="str">
-        <v/>
+        <v>jesujobailesanmi@gmail.com</v>
       </c>
       <c r="H31" t="str">
-        <v/>
+        <v>+27 76 231 2892</v>
       </c>
       <c r="I31" t="str">
         <v>Yes</v>
@@ -1498,19 +1498,19 @@
         <v>Jesuloba Ilesanmi</v>
       </c>
       <c r="D32" t="str">
-        <v>pending</v>
+        <v>submitted</v>
       </c>
       <c r="E32" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="F32" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="G32" t="str">
-        <v/>
+        <v>jesuloba.ilesanmi@gmail.com</v>
       </c>
       <c r="H32" t="str">
-        <v/>
+        <v>+27 63 535 8475</v>
       </c>
       <c r="I32" t="str">
         <v>Yes</v>
@@ -1533,19 +1533,19 @@
         <v>Jesutowo Ilesanmi</v>
       </c>
       <c r="D33" t="str">
-        <v>pending</v>
+        <v>submitted</v>
       </c>
       <c r="E33" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="F33" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="G33" t="str">
-        <v/>
+        <v>towo.ilez@gmail.com</v>
       </c>
       <c r="H33" t="str">
-        <v/>
+        <v>+27 83 319 2130</v>
       </c>
       <c r="I33" t="str">
         <v>Yes</v>
@@ -1568,19 +1568,19 @@
         <v>Limpho Ilesanmi</v>
       </c>
       <c r="D34" t="str">
-        <v>pending</v>
+        <v>submitted</v>
       </c>
       <c r="E34" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="F34" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="G34" t="str">
-        <v/>
+        <v>limphoilesanmi@gmail.com</v>
       </c>
       <c r="H34" t="str">
-        <v/>
+        <v>+27 83 410 6360</v>
       </c>
       <c r="I34" t="str">
         <v>Yes</v>
@@ -1673,19 +1673,19 @@
         <v>Baile Lefenya</v>
       </c>
       <c r="D37" t="str">
-        <v>pending</v>
+        <v>submitted</v>
       </c>
       <c r="E37" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="F37" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="G37" t="str">
-        <v/>
+        <v>Kamolefenya@gmail.com</v>
       </c>
       <c r="H37" t="str">
-        <v/>
+        <v>0840168370</v>
       </c>
       <c r="I37" t="str">
         <v>Yes</v>
@@ -1708,19 +1708,19 @@
         <v>Kamo Lefenya</v>
       </c>
       <c r="D38" t="str">
-        <v>pending</v>
+        <v>submitted</v>
       </c>
       <c r="E38" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="F38" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="G38" t="str">
-        <v/>
+        <v>Kamolefenya@gmail.com</v>
       </c>
       <c r="H38" t="str">
-        <v/>
+        <v>0722444544</v>
       </c>
       <c r="I38" t="str">
         <v>Yes</v>
@@ -1848,19 +1848,19 @@
         <v>Mr Malatjie</v>
       </c>
       <c r="D42" t="str">
-        <v>pending</v>
+        <v>submitted</v>
       </c>
       <c r="E42" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="F42" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="G42" t="str">
-        <v/>
+        <v>kmalatji@homecomingza.com</v>
       </c>
       <c r="H42" t="str">
-        <v/>
+        <v>0840981501</v>
       </c>
       <c r="I42" t="str">
         <v>Yes</v>
@@ -1883,19 +1883,19 @@
         <v>Mrs Malatjie</v>
       </c>
       <c r="D43" t="str">
-        <v>pending</v>
+        <v>submitted</v>
       </c>
       <c r="E43" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="F43" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="G43" t="str">
-        <v/>
+        <v>tmaselav@gmail.com</v>
       </c>
       <c r="H43" t="str">
-        <v/>
+        <v>0647578008</v>
       </c>
       <c r="I43" t="str">
         <v>Yes</v>
@@ -2373,19 +2373,19 @@
         <v>Josephine Ogboro</v>
       </c>
       <c r="D57" t="str">
-        <v>pending</v>
+        <v>submitted</v>
       </c>
       <c r="E57" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="F57" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="G57" t="str">
-        <v/>
+        <v>jojompho@gmail.com</v>
       </c>
       <c r="H57" t="str">
-        <v/>
+        <v>0624025474</v>
       </c>
       <c r="I57" t="str">
         <v>Yes</v>
@@ -2513,19 +2513,19 @@
         <v>Laolu Ojobaro</v>
       </c>
       <c r="D61" t="str">
-        <v>pending</v>
+        <v>submitted</v>
       </c>
       <c r="E61" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="F61" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="G61" t="str">
-        <v/>
+        <v>laoluojobaro@gmail.com</v>
       </c>
       <c r="H61" t="str">
-        <v/>
+        <v>0722965051</v>
       </c>
       <c r="I61" t="str">
         <v>Yes</v>
@@ -2548,19 +2548,19 @@
         <v>Ore Ojobaro</v>
       </c>
       <c r="D62" t="str">
-        <v>pending</v>
+        <v>submitted</v>
       </c>
       <c r="E62" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="F62" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="G62" t="str">
-        <v/>
+        <v>oreojobaro@gmail.com</v>
       </c>
       <c r="H62" t="str">
-        <v/>
+        <v>0810897848</v>
       </c>
       <c r="I62" t="str">
         <v>Yes</v>
@@ -3388,19 +3388,19 @@
         <v>Emmanuel Williams</v>
       </c>
       <c r="D86" t="str">
-        <v>pending</v>
+        <v>submitted</v>
       </c>
       <c r="E86" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="F86" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="G86" t="str">
-        <v/>
+        <v>emmanuelwilliams449@gmail.com</v>
       </c>
       <c r="H86" t="str">
-        <v/>
+        <v>0662365872</v>
       </c>
       <c r="I86" t="str">
         <v>Yes</v>
@@ -3423,19 +3423,19 @@
         <v>Tinu Williams</v>
       </c>
       <c r="D87" t="str">
-        <v>pending</v>
+        <v>submitted</v>
       </c>
       <c r="E87" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="F87" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="G87" t="str">
-        <v/>
+        <v>williamstinuade02@gmail.com</v>
       </c>
       <c r="H87" t="str">
-        <v/>
+        <v>0659149665</v>
       </c>
       <c r="I87" t="str">
         <v>Yes</v>
@@ -4893,19 +4893,19 @@
         <v>Mr Ilesanmi</v>
       </c>
       <c r="D129" t="str">
-        <v>pending</v>
+        <v>submitted</v>
       </c>
       <c r="E129" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="F129" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="G129" t="str">
-        <v/>
+        <v>taiwoiles@gmail.com</v>
       </c>
       <c r="H129" t="str">
-        <v/>
+        <v>+27799202197</v>
       </c>
       <c r="I129" t="str">
         <v>Yes</v>
@@ -4928,19 +4928,19 @@
         <v>Mrs Ilesanmi</v>
       </c>
       <c r="D130" t="str">
-        <v>pending</v>
+        <v>submitted</v>
       </c>
       <c r="E130" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="F130" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="G130" t="str">
-        <v/>
+        <v>ilesanmia25@gmail.com</v>
       </c>
       <c r="H130" t="str">
-        <v/>
+        <v>+27 83 576 9263</v>
       </c>
       <c r="I130" t="str">
         <v>Yes</v>
@@ -5383,19 +5383,19 @@
         <v>Mapule Makabane</v>
       </c>
       <c r="D143" t="str">
-        <v>pending</v>
+        <v>submitted</v>
       </c>
       <c r="E143" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="F143" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="G143" t="str">
-        <v/>
+        <v>missmahabane12@gmail.com</v>
       </c>
       <c r="H143" t="str">
-        <v/>
+        <v>0834745473</v>
       </c>
       <c r="I143" t="str">
         <v>Yes</v>
@@ -6713,19 +6713,19 @@
         <v>Mrs Patience Ossai</v>
       </c>
       <c r="D181" t="str">
-        <v>pending</v>
+        <v>submitted</v>
       </c>
       <c r="E181" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="F181" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="G181" t="str">
-        <v/>
+        <v>ndidiossai123@gmail.com</v>
       </c>
       <c r="H181" t="str">
-        <v/>
+        <v>0727343045</v>
       </c>
       <c r="I181" t="str">
         <v>Yes</v>
@@ -6827,10 +6827,10 @@
         <v>Yes</v>
       </c>
       <c r="G184" t="str">
-        <v/>
+        <v>purpleyolanda01@gmail.com</v>
       </c>
       <c r="H184" t="str">
-        <v/>
+        <v>0747615576</v>
       </c>
       <c r="I184" t="str">
         <v>Yes</v>
@@ -6862,10 +6862,10 @@
         <v>Yes</v>
       </c>
       <c r="G185" t="str">
-        <v/>
+        <v>purpleyolanda01@gmail.com</v>
       </c>
       <c r="H185" t="str">
-        <v/>
+        <v>0623526950</v>
       </c>
       <c r="I185" t="str">
         <v>Yes</v>
@@ -6897,10 +6897,10 @@
         <v>Yes</v>
       </c>
       <c r="G186" t="str">
-        <v/>
+        <v>purpleyolanda01@gmail.com</v>
       </c>
       <c r="H186" t="str">
-        <v/>
+        <v>065 955 6099</v>
       </c>
       <c r="I186" t="str">
         <v>Yes</v>
@@ -7599,7 +7599,7 @@
         <v>Ayo Abe</v>
       </c>
       <c r="D2" t="str">
-        <v>pending</v>
+        <v>submitted</v>
       </c>
       <c r="E2" t="str">
         <v>No</v>
@@ -7634,19 +7634,19 @@
         <v>Pelumi Abe</v>
       </c>
       <c r="D3" t="str">
-        <v>pending</v>
+        <v>submitted</v>
       </c>
       <c r="E3" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="F3" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="G3" t="str">
-        <v/>
+        <v>pelumiabe@rocketmail.com</v>
       </c>
       <c r="H3" t="str">
-        <v/>
+        <v>0798401428</v>
       </c>
       <c r="I3" t="str">
         <v>Yes</v>
@@ -7669,7 +7669,7 @@
         <v>Victoria Abe</v>
       </c>
       <c r="D4" t="str">
-        <v>pending</v>
+        <v>submitted</v>
       </c>
       <c r="E4" t="str">
         <v>No</v>
@@ -8579,19 +8579,19 @@
         <v>Jesudara Ilesanmi</v>
       </c>
       <c r="D30" t="str">
-        <v>pending</v>
+        <v>submitted</v>
       </c>
       <c r="E30" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="F30" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="G30" t="str">
-        <v/>
+        <v>towo.ilez@gmail.com</v>
       </c>
       <c r="H30" t="str">
-        <v/>
+        <v>+27 63 819 9263</v>
       </c>
       <c r="I30" t="str">
         <v>Yes</v>
@@ -8614,19 +8614,19 @@
         <v>Jesujoba Ilesanmi</v>
       </c>
       <c r="D31" t="str">
-        <v>pending</v>
+        <v>submitted</v>
       </c>
       <c r="E31" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="F31" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="G31" t="str">
-        <v/>
+        <v>jesujobailesanmi@gmail.com</v>
       </c>
       <c r="H31" t="str">
-        <v/>
+        <v>+27 76 231 2892</v>
       </c>
       <c r="I31" t="str">
         <v>Yes</v>
@@ -8649,19 +8649,19 @@
         <v>Jesuloba Ilesanmi</v>
       </c>
       <c r="D32" t="str">
-        <v>pending</v>
+        <v>submitted</v>
       </c>
       <c r="E32" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="F32" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="G32" t="str">
-        <v/>
+        <v>jesuloba.ilesanmi@gmail.com</v>
       </c>
       <c r="H32" t="str">
-        <v/>
+        <v>+27 63 535 8475</v>
       </c>
       <c r="I32" t="str">
         <v>Yes</v>
@@ -8684,19 +8684,19 @@
         <v>Jesutowo Ilesanmi</v>
       </c>
       <c r="D33" t="str">
-        <v>pending</v>
+        <v>submitted</v>
       </c>
       <c r="E33" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="F33" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="G33" t="str">
-        <v/>
+        <v>towo.ilez@gmail.com</v>
       </c>
       <c r="H33" t="str">
-        <v/>
+        <v>+27 83 319 2130</v>
       </c>
       <c r="I33" t="str">
         <v>Yes</v>
@@ -8719,19 +8719,19 @@
         <v>Limpho Ilesanmi</v>
       </c>
       <c r="D34" t="str">
-        <v>pending</v>
+        <v>submitted</v>
       </c>
       <c r="E34" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="F34" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="G34" t="str">
-        <v/>
+        <v>limphoilesanmi@gmail.com</v>
       </c>
       <c r="H34" t="str">
-        <v/>
+        <v>+27 83 410 6360</v>
       </c>
       <c r="I34" t="str">
         <v>Yes</v>
@@ -8824,19 +8824,19 @@
         <v>Baile Lefenya</v>
       </c>
       <c r="D37" t="str">
-        <v>pending</v>
+        <v>submitted</v>
       </c>
       <c r="E37" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="F37" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="G37" t="str">
-        <v/>
+        <v>Kamolefenya@gmail.com</v>
       </c>
       <c r="H37" t="str">
-        <v/>
+        <v>0840168370</v>
       </c>
       <c r="I37" t="str">
         <v>Yes</v>
@@ -8859,19 +8859,19 @@
         <v>Kamo Lefenya</v>
       </c>
       <c r="D38" t="str">
-        <v>pending</v>
+        <v>submitted</v>
       </c>
       <c r="E38" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="F38" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="G38" t="str">
-        <v/>
+        <v>Kamolefenya@gmail.com</v>
       </c>
       <c r="H38" t="str">
-        <v/>
+        <v>0722444544</v>
       </c>
       <c r="I38" t="str">
         <v>Yes</v>
@@ -8999,19 +8999,19 @@
         <v>Mr Malatjie</v>
       </c>
       <c r="D42" t="str">
-        <v>pending</v>
+        <v>submitted</v>
       </c>
       <c r="E42" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="F42" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="G42" t="str">
-        <v/>
+        <v>kmalatji@homecomingza.com</v>
       </c>
       <c r="H42" t="str">
-        <v/>
+        <v>0840981501</v>
       </c>
       <c r="I42" t="str">
         <v>Yes</v>
@@ -9034,19 +9034,19 @@
         <v>Mrs Malatjie</v>
       </c>
       <c r="D43" t="str">
-        <v>pending</v>
+        <v>submitted</v>
       </c>
       <c r="E43" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="F43" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="G43" t="str">
-        <v/>
+        <v>tmaselav@gmail.com</v>
       </c>
       <c r="H43" t="str">
-        <v/>
+        <v>0647578008</v>
       </c>
       <c r="I43" t="str">
         <v>Yes</v>
@@ -9524,19 +9524,19 @@
         <v>Josephine Ogboro</v>
       </c>
       <c r="D57" t="str">
-        <v>pending</v>
+        <v>submitted</v>
       </c>
       <c r="E57" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="F57" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="G57" t="str">
-        <v/>
+        <v>jojompho@gmail.com</v>
       </c>
       <c r="H57" t="str">
-        <v/>
+        <v>0624025474</v>
       </c>
       <c r="I57" t="str">
         <v>Yes</v>
@@ -9664,19 +9664,19 @@
         <v>Laolu Ojobaro</v>
       </c>
       <c r="D61" t="str">
-        <v>pending</v>
+        <v>submitted</v>
       </c>
       <c r="E61" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="F61" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="G61" t="str">
-        <v/>
+        <v>laoluojobaro@gmail.com</v>
       </c>
       <c r="H61" t="str">
-        <v/>
+        <v>0722965051</v>
       </c>
       <c r="I61" t="str">
         <v>Yes</v>
@@ -9699,19 +9699,19 @@
         <v>Ore Ojobaro</v>
       </c>
       <c r="D62" t="str">
-        <v>pending</v>
+        <v>submitted</v>
       </c>
       <c r="E62" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="F62" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="G62" t="str">
-        <v/>
+        <v>oreojobaro@gmail.com</v>
       </c>
       <c r="H62" t="str">
-        <v/>
+        <v>0810897848</v>
       </c>
       <c r="I62" t="str">
         <v>Yes</v>
@@ -10539,19 +10539,19 @@
         <v>Emmanuel Williams</v>
       </c>
       <c r="D86" t="str">
-        <v>pending</v>
+        <v>submitted</v>
       </c>
       <c r="E86" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="F86" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="G86" t="str">
-        <v/>
+        <v>emmanuelwilliams449@gmail.com</v>
       </c>
       <c r="H86" t="str">
-        <v/>
+        <v>0662365872</v>
       </c>
       <c r="I86" t="str">
         <v>Yes</v>
@@ -10574,19 +10574,19 @@
         <v>Tinu Williams</v>
       </c>
       <c r="D87" t="str">
-        <v>pending</v>
+        <v>submitted</v>
       </c>
       <c r="E87" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="F87" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="G87" t="str">
-        <v/>
+        <v>williamstinuade02@gmail.com</v>
       </c>
       <c r="H87" t="str">
-        <v/>
+        <v>0659149665</v>
       </c>
       <c r="I87" t="str">
         <v>Yes</v>
@@ -12090,19 +12090,19 @@
         <v>Mr Ilesanmi</v>
       </c>
       <c r="D42" t="str">
-        <v>pending</v>
+        <v>submitted</v>
       </c>
       <c r="E42" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="F42" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="G42" t="str">
-        <v/>
+        <v>taiwoiles@gmail.com</v>
       </c>
       <c r="H42" t="str">
-        <v/>
+        <v>+27799202197</v>
       </c>
       <c r="I42" t="str">
         <v>Yes</v>
@@ -12125,19 +12125,19 @@
         <v>Mrs Ilesanmi</v>
       </c>
       <c r="D43" t="str">
-        <v>pending</v>
+        <v>submitted</v>
       </c>
       <c r="E43" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="F43" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="G43" t="str">
-        <v/>
+        <v>ilesanmia25@gmail.com</v>
       </c>
       <c r="H43" t="str">
-        <v/>
+        <v>+27 83 576 9263</v>
       </c>
       <c r="I43" t="str">
         <v>Yes</v>
@@ -12580,19 +12580,19 @@
         <v>Mapule Makabane</v>
       </c>
       <c r="D56" t="str">
-        <v>pending</v>
+        <v>submitted</v>
       </c>
       <c r="E56" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="F56" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="G56" t="str">
-        <v/>
+        <v>missmahabane12@gmail.com</v>
       </c>
       <c r="H56" t="str">
-        <v/>
+        <v>0834745473</v>
       </c>
       <c r="I56" t="str">
         <v>Yes</v>
@@ -13910,19 +13910,19 @@
         <v>Mrs Patience Ossai</v>
       </c>
       <c r="D94" t="str">
-        <v>pending</v>
+        <v>submitted</v>
       </c>
       <c r="E94" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="F94" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="G94" t="str">
-        <v/>
+        <v>ndidiossai123@gmail.com</v>
       </c>
       <c r="H94" t="str">
-        <v/>
+        <v>0727343045</v>
       </c>
       <c r="I94" t="str">
         <v>Yes</v>
@@ -14024,10 +14024,10 @@
         <v>Yes</v>
       </c>
       <c r="G97" t="str">
-        <v/>
+        <v>purpleyolanda01@gmail.com</v>
       </c>
       <c r="H97" t="str">
-        <v/>
+        <v>0747615576</v>
       </c>
       <c r="I97" t="str">
         <v>Yes</v>
@@ -14059,10 +14059,10 @@
         <v>Yes</v>
       </c>
       <c r="G98" t="str">
-        <v/>
+        <v>purpleyolanda01@gmail.com</v>
       </c>
       <c r="H98" t="str">
-        <v/>
+        <v>0623526950</v>
       </c>
       <c r="I98" t="str">
         <v>Yes</v>
@@ -14094,10 +14094,10 @@
         <v>Yes</v>
       </c>
       <c r="G99" t="str">
-        <v/>
+        <v>purpleyolanda01@gmail.com</v>
       </c>
       <c r="H99" t="str">
-        <v/>
+        <v>065 955 6099</v>
       </c>
       <c r="I99" t="str">
         <v>Yes</v>
@@ -14787,7 +14787,7 @@
         <v>Reception Attending</v>
       </c>
       <c r="B5">
-        <v>29</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6">
@@ -14795,7 +14795,7 @@
         <v>Church Attending</v>
       </c>
       <c r="B6">
-        <v>28</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7">
@@ -14803,7 +14803,7 @@
         <v>Missing Cellphone Numbers</v>
       </c>
       <c r="B7">
-        <v>183</v>
+        <v>161</v>
       </c>
     </row>
     <row r="8">
@@ -14811,7 +14811,7 @@
         <v>Missing Email Addresses</v>
       </c>
       <c r="B8">
-        <v>183</v>
+        <v>161</v>
       </c>
     </row>
   </sheetData>
